--- a/excel/dashboard_ventas.xlsx
+++ b/excel/dashboard_ventas.xlsx
@@ -21,8 +21,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0"/>
-    <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.00"/>
+    <numFmt numFmtId="164" formatCode="#.##0,00 &quot;ARS&quot;"/>
+    <numFmt numFmtId="165" formatCode="#.##0,00 &quot;USD&quot;"/>
   </numFmts>
   <fonts count="5">
     <font>
@@ -897,24 +897,24 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Ventas último mes (ARS)</t>
+          <t>Ventas último mes</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>$125,876,752</t>
+          <t>ARS 122,5 M (USD 80,9 k)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Ventas acumuladas 24m (ARS)</t>
+          <t>Ventas acumuladas 24m</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>$2,461,567,537</t>
+          <t>ARS 2.479,7 M (USD 1,6 M)</t>
         </is>
       </c>
     </row>
@@ -926,7 +926,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>27,972</t>
+          <t>27.227</t>
         </is>
       </c>
     </row>
@@ -938,19 +938,19 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Mayorista San Martín</t>
+          <t>Hipermercado Andino</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Ventas top cliente 12m (ARS)</t>
+          <t>Ventas top cliente 12m</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>$45,632,942</t>
+          <t>ARS 42,4 M (USD 28,0 k)</t>
         </is>
       </c>
     </row>
@@ -1020,16 +1020,16 @@
         </is>
       </c>
       <c r="C2" s="7" t="n">
-        <v>84313411.78</v>
+        <v>81668812.81999999</v>
       </c>
       <c r="D2" s="8" t="n">
-        <v>55668.38</v>
+        <v>53922.27</v>
       </c>
       <c r="E2" s="6" t="n">
-        <v>18736</v>
+        <v>18148</v>
       </c>
       <c r="F2" s="7" t="n">
-        <v>4500.08</v>
+        <v>4500.15</v>
       </c>
     </row>
     <row r="3">
@@ -1044,16 +1044,16 @@
         </is>
       </c>
       <c r="C3" s="7" t="n">
-        <v>83568483.34</v>
+        <v>90532309.43000001</v>
       </c>
       <c r="D3" s="8" t="n">
-        <v>55176.54</v>
+        <v>59774.44</v>
       </c>
       <c r="E3" s="6" t="n">
-        <v>18570</v>
+        <v>20118</v>
       </c>
       <c r="F3" s="7" t="n">
-        <v>4500.19</v>
+        <v>4500.07</v>
       </c>
     </row>
     <row r="4">
@@ -1068,16 +1068,16 @@
         </is>
       </c>
       <c r="C4" s="7" t="n">
-        <v>91107789.3</v>
+        <v>91124622.55</v>
       </c>
       <c r="D4" s="8" t="n">
-        <v>60154.41</v>
+        <v>60165.52</v>
       </c>
       <c r="E4" s="6" t="n">
-        <v>20246</v>
+        <v>20249</v>
       </c>
       <c r="F4" s="7" t="n">
-        <v>4500.04</v>
+        <v>4500.2</v>
       </c>
     </row>
     <row r="5">
@@ -1092,16 +1092,16 @@
         </is>
       </c>
       <c r="C5" s="7" t="n">
-        <v>92821534.43000001</v>
+        <v>89349775.04000001</v>
       </c>
       <c r="D5" s="8" t="n">
-        <v>61285.92</v>
+        <v>58993.67</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>20627</v>
+        <v>19855</v>
       </c>
       <c r="F5" s="7" t="n">
-        <v>4500</v>
+        <v>4500.11</v>
       </c>
     </row>
     <row r="6">
@@ -1116,16 +1116,16 @@
         </is>
       </c>
       <c r="C6" s="7" t="n">
-        <v>93738556.53</v>
+        <v>88787186.20999999</v>
       </c>
       <c r="D6" s="8" t="n">
-        <v>61891.39</v>
+        <v>58622.22</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>20830</v>
+        <v>19730</v>
       </c>
       <c r="F6" s="7" t="n">
-        <v>4500.17</v>
+        <v>4500.11</v>
       </c>
     </row>
     <row r="7">
@@ -1140,16 +1140,16 @@
         </is>
       </c>
       <c r="C7" s="7" t="n">
-        <v>89671930.81999999</v>
+        <v>95712723.36</v>
       </c>
       <c r="D7" s="8" t="n">
-        <v>59206.37</v>
+        <v>63194.84</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>19927</v>
+        <v>21269</v>
       </c>
       <c r="F7" s="7" t="n">
-        <v>4500.02</v>
+        <v>4500.1</v>
       </c>
     </row>
     <row r="8">
@@ -1164,16 +1164,16 @@
         </is>
       </c>
       <c r="C8" s="7" t="n">
-        <v>92427457.55</v>
+        <v>94581311.72</v>
       </c>
       <c r="D8" s="8" t="n">
-        <v>61025.72</v>
+        <v>62447.82</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>20539</v>
+        <v>21018</v>
       </c>
       <c r="F8" s="7" t="n">
-        <v>4500.1</v>
+        <v>4500.01</v>
       </c>
     </row>
     <row r="9">
@@ -1188,16 +1188,16 @@
         </is>
       </c>
       <c r="C9" s="7" t="n">
-        <v>92969836.11</v>
+        <v>94141595.86</v>
       </c>
       <c r="D9" s="8" t="n">
-        <v>61383.83</v>
+        <v>62157.49</v>
       </c>
       <c r="E9" s="6" t="n">
-        <v>20659</v>
+        <v>20920</v>
       </c>
       <c r="F9" s="7" t="n">
-        <v>4500.21</v>
+        <v>4500.08</v>
       </c>
     </row>
     <row r="10">
@@ -1212,16 +1212,16 @@
         </is>
       </c>
       <c r="C10" s="7" t="n">
-        <v>97185323.59</v>
+        <v>93174456.20999999</v>
       </c>
       <c r="D10" s="8" t="n">
-        <v>64167.13</v>
+        <v>61518.93</v>
       </c>
       <c r="E10" s="6" t="n">
-        <v>21596</v>
+        <v>20705</v>
       </c>
       <c r="F10" s="7" t="n">
-        <v>4500.15</v>
+        <v>4500.09</v>
       </c>
     </row>
     <row r="11">
@@ -1236,16 +1236,16 @@
         </is>
       </c>
       <c r="C11" s="7" t="n">
-        <v>98817193.93000001</v>
+        <v>101923737.7</v>
       </c>
       <c r="D11" s="8" t="n">
-        <v>65244.58</v>
+        <v>67295.69</v>
       </c>
       <c r="E11" s="6" t="n">
-        <v>21959</v>
+        <v>22649</v>
       </c>
       <c r="F11" s="7" t="n">
-        <v>4500.08</v>
+        <v>4500.14</v>
       </c>
     </row>
     <row r="12">
@@ -1260,16 +1260,16 @@
         </is>
       </c>
       <c r="C12" s="7" t="n">
-        <v>99373221.68000001</v>
+        <v>98707548.68000001</v>
       </c>
       <c r="D12" s="8" t="n">
-        <v>65611.7</v>
+        <v>65172.19</v>
       </c>
       <c r="E12" s="6" t="n">
-        <v>22082</v>
+        <v>21935</v>
       </c>
       <c r="F12" s="7" t="n">
-        <v>4500.19</v>
+        <v>4500</v>
       </c>
     </row>
     <row r="13">
@@ -1284,16 +1284,16 @@
         </is>
       </c>
       <c r="C13" s="7" t="n">
-        <v>97034059.73999999</v>
+        <v>101470626.32</v>
       </c>
       <c r="D13" s="8" t="n">
-        <v>64067.26</v>
+        <v>66996.53</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>21563</v>
+        <v>22549</v>
       </c>
       <c r="F13" s="7" t="n">
-        <v>4500.03</v>
+        <v>4500.01</v>
       </c>
     </row>
     <row r="14">
@@ -1308,16 +1308,16 @@
         </is>
       </c>
       <c r="C14" s="7" t="n">
-        <v>100799478.55</v>
+        <v>100482420.4</v>
       </c>
       <c r="D14" s="8" t="n">
-        <v>66553.39999999999</v>
+        <v>66344.06</v>
       </c>
       <c r="E14" s="6" t="n">
-        <v>22399</v>
+        <v>22329</v>
       </c>
       <c r="F14" s="7" t="n">
-        <v>4500.18</v>
+        <v>4500.09</v>
       </c>
     </row>
     <row r="15">
@@ -1332,16 +1332,16 @@
         </is>
       </c>
       <c r="C15" s="7" t="n">
-        <v>100846835.29</v>
+        <v>102613873.4</v>
       </c>
       <c r="D15" s="8" t="n">
-        <v>66584.66</v>
+        <v>67751.36</v>
       </c>
       <c r="E15" s="6" t="n">
-        <v>22410</v>
+        <v>22803</v>
       </c>
       <c r="F15" s="7" t="n">
-        <v>4500.08</v>
+        <v>4500.02</v>
       </c>
     </row>
     <row r="16">
@@ -1356,16 +1356,16 @@
         </is>
       </c>
       <c r="C16" s="7" t="n">
-        <v>106483434.72</v>
+        <v>105363328.6</v>
       </c>
       <c r="D16" s="8" t="n">
-        <v>70306.25999999999</v>
+        <v>69566.7</v>
       </c>
       <c r="E16" s="6" t="n">
-        <v>23662</v>
+        <v>23414</v>
       </c>
       <c r="F16" s="7" t="n">
-        <v>4500.19</v>
+        <v>4500.01</v>
       </c>
     </row>
     <row r="17">
@@ -1380,16 +1380,16 @@
         </is>
       </c>
       <c r="C17" s="7" t="n">
-        <v>105185005.83</v>
+        <v>104795570.44</v>
       </c>
       <c r="D17" s="8" t="n">
-        <v>69448.96000000001</v>
+        <v>69191.84</v>
       </c>
       <c r="E17" s="6" t="n">
-        <v>23374</v>
+        <v>23287</v>
       </c>
       <c r="F17" s="7" t="n">
-        <v>4500.09</v>
+        <v>4500.17</v>
       </c>
     </row>
     <row r="18">
@@ -1404,16 +1404,16 @@
         </is>
       </c>
       <c r="C18" s="7" t="n">
-        <v>105024748.08</v>
+        <v>113951288.5</v>
       </c>
       <c r="D18" s="8" t="n">
-        <v>69343.14999999999</v>
+        <v>75236.95</v>
       </c>
       <c r="E18" s="6" t="n">
-        <v>23338</v>
+        <v>25322</v>
       </c>
       <c r="F18" s="7" t="n">
-        <v>4500.16</v>
+        <v>4500.09</v>
       </c>
     </row>
     <row r="19">
@@ -1428,16 +1428,16 @@
         </is>
       </c>
       <c r="C19" s="7" t="n">
-        <v>111283493.88</v>
+        <v>116014178.47</v>
       </c>
       <c r="D19" s="8" t="n">
-        <v>73475.52</v>
+        <v>76598.98</v>
       </c>
       <c r="E19" s="6" t="n">
-        <v>24729</v>
+        <v>25780</v>
       </c>
       <c r="F19" s="7" t="n">
-        <v>4500.12</v>
+        <v>4500.16</v>
       </c>
     </row>
     <row r="20">
@@ -1452,16 +1452,16 @@
         </is>
       </c>
       <c r="C20" s="7" t="n">
-        <v>116165089.47</v>
+        <v>113103787.24</v>
       </c>
       <c r="D20" s="8" t="n">
-        <v>76698.62</v>
+        <v>74677.38</v>
       </c>
       <c r="E20" s="6" t="n">
-        <v>25814</v>
+        <v>25134</v>
       </c>
       <c r="F20" s="7" t="n">
-        <v>4500.08</v>
+        <v>4500.03</v>
       </c>
     </row>
     <row r="21">
@@ -1476,16 +1476,16 @@
         </is>
       </c>
       <c r="C21" s="7" t="n">
-        <v>119175661.42</v>
+        <v>115311899.11</v>
       </c>
       <c r="D21" s="8" t="n">
-        <v>78686.37</v>
+        <v>76135.3</v>
       </c>
       <c r="E21" s="6" t="n">
-        <v>26483</v>
+        <v>25624</v>
       </c>
       <c r="F21" s="7" t="n">
-        <v>4500.08</v>
+        <v>4500.15</v>
       </c>
     </row>
     <row r="22">
@@ -1500,16 +1500,16 @@
         </is>
       </c>
       <c r="C22" s="7" t="n">
-        <v>117306657.4</v>
+        <v>119808151.36</v>
       </c>
       <c r="D22" s="8" t="n">
-        <v>77452.35000000001</v>
+        <v>79103.97</v>
       </c>
       <c r="E22" s="6" t="n">
-        <v>26068</v>
+        <v>26624</v>
       </c>
       <c r="F22" s="7" t="n">
-        <v>4500.03</v>
+        <v>4500.01</v>
       </c>
     </row>
     <row r="23">
@@ -1524,16 +1524,16 @@
         </is>
       </c>
       <c r="C23" s="7" t="n">
-        <v>118010807.17</v>
+        <v>120357452.44</v>
       </c>
       <c r="D23" s="8" t="n">
-        <v>77917.27</v>
+        <v>79466.64999999999</v>
       </c>
       <c r="E23" s="6" t="n">
-        <v>26224</v>
+        <v>26746</v>
       </c>
       <c r="F23" s="7" t="n">
-        <v>4500.11</v>
+        <v>4500.02</v>
       </c>
     </row>
     <row r="24">
@@ -1548,16 +1548,16 @@
         </is>
       </c>
       <c r="C24" s="7" t="n">
-        <v>122380774.57</v>
+        <v>124227570.28</v>
       </c>
       <c r="D24" s="8" t="n">
-        <v>80802.56</v>
+        <v>82021.92</v>
       </c>
       <c r="E24" s="6" t="n">
-        <v>27195</v>
+        <v>27606</v>
       </c>
       <c r="F24" s="7" t="n">
-        <v>4500.12</v>
+        <v>4500.02</v>
       </c>
     </row>
     <row r="25">
@@ -1572,16 +1572,16 @@
         </is>
       </c>
       <c r="C25" s="7" t="n">
-        <v>125876751.58</v>
+        <v>122521699.98</v>
       </c>
       <c r="D25" s="8" t="n">
-        <v>83110.8</v>
+        <v>80895.61</v>
       </c>
       <c r="E25" s="6" t="n">
-        <v>27972</v>
+        <v>27227</v>
       </c>
       <c r="F25" s="7" t="n">
-        <v>4500.1</v>
+        <v>4500.01</v>
       </c>
     </row>
   </sheetData>
@@ -1643,10 +1643,10 @@
         </is>
       </c>
       <c r="D2" s="7" t="n">
-        <v>49490897.24</v>
+        <v>47450006.76</v>
       </c>
       <c r="E2" s="6" t="n">
-        <v>32676.63</v>
+        <v>31329.12</v>
       </c>
     </row>
     <row r="3">
@@ -1666,10 +1666,10 @@
         </is>
       </c>
       <c r="D3" s="7" t="n">
-        <v>35295522.21</v>
+        <v>32883497.94</v>
       </c>
       <c r="E3" s="6" t="n">
-        <v>23304.06</v>
+        <v>21711.51</v>
       </c>
     </row>
     <row r="4">
@@ -1689,10 +1689,10 @@
         </is>
       </c>
       <c r="D4" s="7" t="n">
-        <v>21836423.79</v>
+        <v>23510624.77</v>
       </c>
       <c r="E4" s="6" t="n">
-        <v>14417.62</v>
+        <v>15523.02</v>
       </c>
     </row>
     <row r="5">
@@ -1712,10 +1712,10 @@
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>21218909.7</v>
+        <v>18484090.91</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>14009.9</v>
+        <v>12204.22</v>
       </c>
     </row>
   </sheetData>
@@ -1777,10 +1777,10 @@
         </is>
       </c>
       <c r="D2" s="7" t="n">
-        <v>30352757.26</v>
+        <v>26745334.93</v>
       </c>
       <c r="E2" s="6" t="n">
-        <v>20040.57</v>
+        <v>17658.75</v>
       </c>
     </row>
     <row r="3">
@@ -1800,10 +1800,10 @@
         </is>
       </c>
       <c r="D3" s="7" t="n">
-        <v>21496515.73</v>
+        <v>20968753.87</v>
       </c>
       <c r="E3" s="6" t="n">
-        <v>14193.19</v>
+        <v>13844.73</v>
       </c>
     </row>
     <row r="4">
@@ -1823,10 +1823,10 @@
         </is>
       </c>
       <c r="D4" s="7" t="n">
-        <v>17803431.5</v>
+        <v>16313659.94</v>
       </c>
       <c r="E4" s="6" t="n">
-        <v>11754.81</v>
+        <v>10771.18</v>
       </c>
     </row>
     <row r="5">
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>19671358.19</v>
+        <v>17679969.25</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>12988.12</v>
+        <v>11673.29</v>
       </c>
     </row>
     <row r="6">
@@ -1869,10 +1869,10 @@
         </is>
       </c>
       <c r="D6" s="7" t="n">
-        <v>20474614.51</v>
+        <v>19497979.87</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>13518.47</v>
+        <v>12873.65</v>
       </c>
     </row>
     <row r="7">
@@ -1892,10 +1892,10 @@
         </is>
       </c>
       <c r="D7" s="7" t="n">
-        <v>18912632.84</v>
+        <v>19852960.82</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>12487.17</v>
+        <v>13108.02</v>
       </c>
     </row>
   </sheetData>
@@ -1953,19 +1953,19 @@
       </c>
       <c r="B2" s="6" t="inlineStr">
         <is>
-          <t>CLI-106</t>
+          <t>CLI-109</t>
         </is>
       </c>
       <c r="C2" s="6" t="inlineStr">
         <is>
-          <t>Mayorista San Martín</t>
+          <t>Hipermercado Andino</t>
         </is>
       </c>
       <c r="D2" s="7" t="n">
-        <v>45632942.17</v>
-      </c>
-      <c r="E2" s="6" t="n">
-        <v>30129.39</v>
+        <v>42430941.31</v>
+      </c>
+      <c r="E2" s="8" t="n">
+        <v>28015.26</v>
       </c>
       <c r="F2" s="6" t="n">
         <v>1</v>
@@ -1988,10 +1988,10 @@
         </is>
       </c>
       <c r="D3" s="7" t="n">
-        <v>43655745.19</v>
-      </c>
-      <c r="E3" s="6" t="n">
-        <v>28823.94</v>
+        <v>36393991.89</v>
+      </c>
+      <c r="E3" s="8" t="n">
+        <v>24029.33</v>
       </c>
       <c r="F3" s="6" t="n">
         <v>2</v>
@@ -2005,19 +2005,19 @@
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>CLI-102</t>
+          <t>CLI-106</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>Distribuidora La Ribera S.R.L.</t>
+          <t>Mayorista San Martín</t>
         </is>
       </c>
       <c r="D4" s="7" t="n">
-        <v>43104969.64</v>
-      </c>
-      <c r="E4" s="6" t="n">
-        <v>28460.29</v>
+        <v>35001793.28</v>
+      </c>
+      <c r="E4" s="8" t="n">
+        <v>23110.12</v>
       </c>
       <c r="F4" s="6" t="n">
         <v>3</v>
@@ -2031,19 +2031,19 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>CLI-108</t>
+          <t>CLI-105</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>Bodegón Central</t>
+          <t>Mercado Online Pampero</t>
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>41539781.03</v>
-      </c>
-      <c r="E5" s="6" t="n">
-        <v>27426.86</v>
+        <v>33152581.38</v>
+      </c>
+      <c r="E5" s="8" t="n">
+        <v>21889.17</v>
       </c>
       <c r="F5" s="6" t="n">
         <v>4</v>
@@ -2057,19 +2057,19 @@
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>CLI-104</t>
+          <t>CLI-103</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>Grupo Norte Retail S.A.</t>
+          <t>Almacén El Fogón</t>
         </is>
       </c>
       <c r="D6" s="7" t="n">
-        <v>40440222.55</v>
-      </c>
-      <c r="E6" s="6" t="n">
-        <v>26700.87</v>
+        <v>27902272.21</v>
+      </c>
+      <c r="E6" s="8" t="n">
+        <v>18422.62</v>
       </c>
       <c r="F6" s="6" t="n">
         <v>5</v>
@@ -2092,10 +2092,10 @@
         </is>
       </c>
       <c r="D7" s="7" t="n">
-        <v>30278556.33</v>
-      </c>
-      <c r="E7" s="6" t="n">
-        <v>19991.58</v>
+        <v>27275121.78</v>
+      </c>
+      <c r="E7" s="8" t="n">
+        <v>18008.55</v>
       </c>
       <c r="F7" s="6" t="n">
         <v>6</v>
@@ -2109,19 +2109,19 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>CLI-105</t>
+          <t>CLI-104</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>Mercado Online Pampero</t>
+          <t>Grupo Norte Retail S.A.</t>
         </is>
       </c>
       <c r="D8" s="7" t="n">
-        <v>26937927.25</v>
-      </c>
-      <c r="E8" s="6" t="n">
-        <v>17785.91</v>
+        <v>24440362.48</v>
+      </c>
+      <c r="E8" s="8" t="n">
+        <v>16136.88</v>
       </c>
       <c r="F8" s="6" t="n">
         <v>7</v>
@@ -2135,19 +2135,19 @@
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>CLI-110</t>
+          <t>CLI-108</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>Cadenas del Sur S.A.</t>
+          <t>Bodegón Central</t>
         </is>
       </c>
       <c r="D9" s="7" t="n">
-        <v>22748010.59</v>
-      </c>
-      <c r="E9" s="6" t="n">
-        <v>15019.5</v>
+        <v>21003536.08</v>
+      </c>
+      <c r="E9" s="8" t="n">
+        <v>13867.7</v>
       </c>
       <c r="F9" s="6" t="n">
         <v>8</v>
@@ -2161,19 +2161,19 @@
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>CLI-109</t>
+          <t>CLI-110</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>Hipermercado Andino</t>
+          <t>Cadenas del Sur S.A.</t>
         </is>
       </c>
       <c r="D10" s="7" t="n">
-        <v>22182203.4</v>
-      </c>
-      <c r="E10" s="6" t="n">
-        <v>14645.92</v>
+        <v>19171811.97</v>
+      </c>
+      <c r="E10" s="8" t="n">
+        <v>12658.29</v>
       </c>
       <c r="F10" s="6" t="n">
         <v>9</v>
@@ -2187,19 +2187,19 @@
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>CLI-103</t>
+          <t>CLI-102</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>Almacén El Fogón</t>
+          <t>Distribuidora La Ribera S.R.L.</t>
         </is>
       </c>
       <c r="D11" s="7" t="n">
-        <v>21944906.5</v>
-      </c>
-      <c r="E11" s="6" t="n">
-        <v>14489.24</v>
+        <v>17687122.39</v>
+      </c>
+      <c r="E11" s="8" t="n">
+        <v>11678.02</v>
       </c>
       <c r="F11" s="6" t="n">
         <v>10</v>

--- a/excel/dashboard_ventas.xlsx
+++ b/excel/dashboard_ventas.xlsx
@@ -902,7 +902,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>ARS 122,5 M (USD 80,9 k)</t>
+          <t>ARS 115,6 MM (USD 76,3 k)</t>
         </is>
       </c>
     </row>
@@ -914,7 +914,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>ARS 2.479,7 M (USD 1,6 M)</t>
+          <t>ARS 2,47 mil M (USD 1,6 MM)</t>
         </is>
       </c>
     </row>
@@ -926,7 +926,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>27.227</t>
+          <t>61.757</t>
         </is>
       </c>
     </row>
@@ -938,7 +938,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Hipermercado Andino</t>
+          <t>Almacén El Fogón</t>
         </is>
       </c>
     </row>
@@ -950,7 +950,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>ARS 42,4 M (USD 28,0 k)</t>
+          <t>ARS 71,6 MM (USD 47,3 k)</t>
         </is>
       </c>
     </row>
@@ -1020,16 +1020,16 @@
         </is>
       </c>
       <c r="C2" s="7" t="n">
-        <v>81668812.81999999</v>
+        <v>85948102.23</v>
       </c>
       <c r="D2" s="8" t="n">
-        <v>53922.27</v>
+        <v>56747.7</v>
       </c>
       <c r="E2" s="6" t="n">
-        <v>18148</v>
+        <v>67488</v>
       </c>
       <c r="F2" s="7" t="n">
-        <v>4500.15</v>
+        <v>1273.53</v>
       </c>
     </row>
     <row r="3">
@@ -1044,16 +1044,16 @@
         </is>
       </c>
       <c r="C3" s="7" t="n">
-        <v>90532309.43000001</v>
+        <v>93456965.23</v>
       </c>
       <c r="D3" s="8" t="n">
-        <v>59774.44</v>
+        <v>61705.46</v>
       </c>
       <c r="E3" s="6" t="n">
-        <v>20118</v>
+        <v>60995</v>
       </c>
       <c r="F3" s="7" t="n">
-        <v>4500.07</v>
+        <v>1532.21</v>
       </c>
     </row>
     <row r="4">
@@ -1068,16 +1068,16 @@
         </is>
       </c>
       <c r="C4" s="7" t="n">
-        <v>91124622.55</v>
+        <v>96604256.11</v>
       </c>
       <c r="D4" s="8" t="n">
-        <v>60165.52</v>
+        <v>63783.48</v>
       </c>
       <c r="E4" s="6" t="n">
-        <v>20249</v>
+        <v>69770</v>
       </c>
       <c r="F4" s="7" t="n">
-        <v>4500.2</v>
+        <v>1384.61</v>
       </c>
     </row>
     <row r="5">
@@ -1092,16 +1092,16 @@
         </is>
       </c>
       <c r="C5" s="7" t="n">
-        <v>89349775.04000001</v>
+        <v>96540179.23</v>
       </c>
       <c r="D5" s="8" t="n">
-        <v>58993.67</v>
+        <v>63741.17</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>19855</v>
+        <v>68180</v>
       </c>
       <c r="F5" s="7" t="n">
-        <v>4500.11</v>
+        <v>1415.96</v>
       </c>
     </row>
     <row r="6">
@@ -1116,16 +1116,16 @@
         </is>
       </c>
       <c r="C6" s="7" t="n">
-        <v>88787186.20999999</v>
+        <v>98339809.84</v>
       </c>
       <c r="D6" s="8" t="n">
-        <v>58622.22</v>
+        <v>64929.39</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>19730</v>
+        <v>80652</v>
       </c>
       <c r="F6" s="7" t="n">
-        <v>4500.11</v>
+        <v>1219.31</v>
       </c>
     </row>
     <row r="7">
@@ -1140,16 +1140,16 @@
         </is>
       </c>
       <c r="C7" s="7" t="n">
-        <v>95712723.36</v>
+        <v>100611736.23</v>
       </c>
       <c r="D7" s="8" t="n">
-        <v>63194.84</v>
+        <v>66429.44</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>21269</v>
+        <v>62088</v>
       </c>
       <c r="F7" s="7" t="n">
-        <v>4500.1</v>
+        <v>1620.47</v>
       </c>
     </row>
     <row r="8">
@@ -1164,16 +1164,16 @@
         </is>
       </c>
       <c r="C8" s="7" t="n">
-        <v>94581311.72</v>
+        <v>97624826.17</v>
       </c>
       <c r="D8" s="8" t="n">
-        <v>62447.82</v>
+        <v>64457.32</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>21018</v>
+        <v>64007</v>
       </c>
       <c r="F8" s="7" t="n">
-        <v>4500.01</v>
+        <v>1525.22</v>
       </c>
     </row>
     <row r="9">
@@ -1188,16 +1188,16 @@
         </is>
       </c>
       <c r="C9" s="7" t="n">
-        <v>94141595.86</v>
+        <v>92468453.17</v>
       </c>
       <c r="D9" s="8" t="n">
-        <v>62157.49</v>
+        <v>61052.79</v>
       </c>
       <c r="E9" s="6" t="n">
-        <v>20920</v>
+        <v>72610</v>
       </c>
       <c r="F9" s="7" t="n">
-        <v>4500.08</v>
+        <v>1273.49</v>
       </c>
     </row>
     <row r="10">
@@ -1212,16 +1212,16 @@
         </is>
       </c>
       <c r="C10" s="7" t="n">
-        <v>93174456.20999999</v>
+        <v>87387060.17</v>
       </c>
       <c r="D10" s="8" t="n">
-        <v>61518.93</v>
+        <v>57697.78</v>
       </c>
       <c r="E10" s="6" t="n">
-        <v>20705</v>
+        <v>65928</v>
       </c>
       <c r="F10" s="7" t="n">
-        <v>4500.09</v>
+        <v>1325.49</v>
       </c>
     </row>
     <row r="11">
@@ -1236,16 +1236,16 @@
         </is>
       </c>
       <c r="C11" s="7" t="n">
-        <v>101923737.7</v>
+        <v>89208085.03</v>
       </c>
       <c r="D11" s="8" t="n">
-        <v>67295.69</v>
+        <v>58900.12</v>
       </c>
       <c r="E11" s="6" t="n">
-        <v>22649</v>
+        <v>53043</v>
       </c>
       <c r="F11" s="7" t="n">
-        <v>4500.14</v>
+        <v>1681.81</v>
       </c>
     </row>
     <row r="12">
@@ -1260,16 +1260,16 @@
         </is>
       </c>
       <c r="C12" s="7" t="n">
-        <v>98707548.68000001</v>
+        <v>91347414.59</v>
       </c>
       <c r="D12" s="8" t="n">
-        <v>65172.19</v>
+        <v>60312.62</v>
       </c>
       <c r="E12" s="6" t="n">
-        <v>21935</v>
+        <v>58951</v>
       </c>
       <c r="F12" s="7" t="n">
-        <v>4500</v>
+        <v>1549.55</v>
       </c>
     </row>
     <row r="13">
@@ -1284,16 +1284,16 @@
         </is>
       </c>
       <c r="C13" s="7" t="n">
-        <v>101470626.32</v>
+        <v>92502408.31999999</v>
       </c>
       <c r="D13" s="8" t="n">
-        <v>66996.53</v>
+        <v>61075.21</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>22549</v>
+        <v>58959</v>
       </c>
       <c r="F13" s="7" t="n">
-        <v>4500.01</v>
+        <v>1568.93</v>
       </c>
     </row>
     <row r="14">
@@ -1308,16 +1308,16 @@
         </is>
       </c>
       <c r="C14" s="7" t="n">
-        <v>100482420.4</v>
+        <v>104481947.53</v>
       </c>
       <c r="D14" s="8" t="n">
-        <v>66344.06</v>
+        <v>68984.77</v>
       </c>
       <c r="E14" s="6" t="n">
-        <v>22329</v>
+        <v>63324</v>
       </c>
       <c r="F14" s="7" t="n">
-        <v>4500.09</v>
+        <v>1649.96</v>
       </c>
     </row>
     <row r="15">
@@ -1332,16 +1332,16 @@
         </is>
       </c>
       <c r="C15" s="7" t="n">
-        <v>102613873.4</v>
+        <v>109110744.16</v>
       </c>
       <c r="D15" s="8" t="n">
-        <v>67751.36</v>
+        <v>72040.95</v>
       </c>
       <c r="E15" s="6" t="n">
-        <v>22803</v>
+        <v>66227</v>
       </c>
       <c r="F15" s="7" t="n">
-        <v>4500.02</v>
+        <v>1647.53</v>
       </c>
     </row>
     <row r="16">
@@ -1356,16 +1356,16 @@
         </is>
       </c>
       <c r="C16" s="7" t="n">
-        <v>105363328.6</v>
+        <v>114388733.68</v>
       </c>
       <c r="D16" s="8" t="n">
-        <v>69566.7</v>
+        <v>75525.78</v>
       </c>
       <c r="E16" s="6" t="n">
-        <v>23414</v>
+        <v>80731</v>
       </c>
       <c r="F16" s="7" t="n">
-        <v>4500.01</v>
+        <v>1416.91</v>
       </c>
     </row>
     <row r="17">
@@ -1380,16 +1380,16 @@
         </is>
       </c>
       <c r="C17" s="7" t="n">
-        <v>104795570.44</v>
+        <v>125638826.49</v>
       </c>
       <c r="D17" s="8" t="n">
-        <v>69191.84</v>
+        <v>82953.71000000001</v>
       </c>
       <c r="E17" s="6" t="n">
-        <v>23287</v>
+        <v>69178</v>
       </c>
       <c r="F17" s="7" t="n">
-        <v>4500.17</v>
+        <v>1816.17</v>
       </c>
     </row>
     <row r="18">
@@ -1404,16 +1404,16 @@
         </is>
       </c>
       <c r="C18" s="7" t="n">
-        <v>113951288.5</v>
+        <v>124172393.29</v>
       </c>
       <c r="D18" s="8" t="n">
-        <v>75236.95</v>
+        <v>81985.49000000001</v>
       </c>
       <c r="E18" s="6" t="n">
-        <v>25322</v>
+        <v>64593</v>
       </c>
       <c r="F18" s="7" t="n">
-        <v>4500.09</v>
+        <v>1922.38</v>
       </c>
     </row>
     <row r="19">
@@ -1428,16 +1428,16 @@
         </is>
       </c>
       <c r="C19" s="7" t="n">
-        <v>116014178.47</v>
+        <v>115933339.95</v>
       </c>
       <c r="D19" s="8" t="n">
-        <v>76598.98</v>
+        <v>76545.61</v>
       </c>
       <c r="E19" s="6" t="n">
-        <v>25780</v>
+        <v>92129</v>
       </c>
       <c r="F19" s="7" t="n">
-        <v>4500.16</v>
+        <v>1258.38</v>
       </c>
     </row>
     <row r="20">
@@ -1452,16 +1452,16 @@
         </is>
       </c>
       <c r="C20" s="7" t="n">
-        <v>113103787.24</v>
+        <v>115928513.01</v>
       </c>
       <c r="D20" s="8" t="n">
-        <v>74677.38</v>
+        <v>76542.42</v>
       </c>
       <c r="E20" s="6" t="n">
-        <v>25134</v>
+        <v>80273</v>
       </c>
       <c r="F20" s="7" t="n">
-        <v>4500.03</v>
+        <v>1444.18</v>
       </c>
     </row>
     <row r="21">
@@ -1476,16 +1476,16 @@
         </is>
       </c>
       <c r="C21" s="7" t="n">
-        <v>115311899.11</v>
+        <v>110781815.76</v>
       </c>
       <c r="D21" s="8" t="n">
-        <v>76135.3</v>
+        <v>73144.28999999999</v>
       </c>
       <c r="E21" s="6" t="n">
-        <v>25624</v>
+        <v>67880</v>
       </c>
       <c r="F21" s="7" t="n">
-        <v>4500.15</v>
+        <v>1632.02</v>
       </c>
     </row>
     <row r="22">
@@ -1500,16 +1500,16 @@
         </is>
       </c>
       <c r="C22" s="7" t="n">
-        <v>119808151.36</v>
+        <v>104095048.4</v>
       </c>
       <c r="D22" s="8" t="n">
-        <v>79103.97</v>
+        <v>68729.31</v>
       </c>
       <c r="E22" s="6" t="n">
-        <v>26624</v>
+        <v>67161</v>
       </c>
       <c r="F22" s="7" t="n">
-        <v>4500.01</v>
+        <v>1549.93</v>
       </c>
     </row>
     <row r="23">
@@ -1524,16 +1524,16 @@
         </is>
       </c>
       <c r="C23" s="7" t="n">
-        <v>120357452.44</v>
+        <v>102244861.39</v>
       </c>
       <c r="D23" s="8" t="n">
-        <v>79466.64999999999</v>
+        <v>67507.72</v>
       </c>
       <c r="E23" s="6" t="n">
-        <v>26746</v>
+        <v>66610</v>
       </c>
       <c r="F23" s="7" t="n">
-        <v>4500.02</v>
+        <v>1534.98</v>
       </c>
     </row>
     <row r="24">
@@ -1548,16 +1548,16 @@
         </is>
       </c>
       <c r="C24" s="7" t="n">
-        <v>124227570.28</v>
+        <v>102848652.28</v>
       </c>
       <c r="D24" s="8" t="n">
-        <v>82021.92</v>
+        <v>67906.37</v>
       </c>
       <c r="E24" s="6" t="n">
-        <v>27606</v>
+        <v>67760</v>
       </c>
       <c r="F24" s="7" t="n">
-        <v>4500.02</v>
+        <v>1517.84</v>
       </c>
     </row>
     <row r="25">
@@ -1572,16 +1572,16 @@
         </is>
       </c>
       <c r="C25" s="7" t="n">
-        <v>122521699.98</v>
+        <v>115618497.41</v>
       </c>
       <c r="D25" s="8" t="n">
-        <v>80895.61</v>
+        <v>76337.73</v>
       </c>
       <c r="E25" s="6" t="n">
-        <v>27227</v>
+        <v>61757</v>
       </c>
       <c r="F25" s="7" t="n">
-        <v>4500.01</v>
+        <v>1872.15</v>
       </c>
     </row>
   </sheetData>
@@ -1643,10 +1643,10 @@
         </is>
       </c>
       <c r="D2" s="7" t="n">
-        <v>47450006.76</v>
+        <v>42060532.94</v>
       </c>
       <c r="E2" s="6" t="n">
-        <v>31329.12</v>
+        <v>27770.69</v>
       </c>
     </row>
     <row r="3">
@@ -1666,10 +1666,10 @@
         </is>
       </c>
       <c r="D3" s="7" t="n">
-        <v>32883497.94</v>
+        <v>31166172.74</v>
       </c>
       <c r="E3" s="6" t="n">
-        <v>21711.51</v>
+        <v>20577.63</v>
       </c>
     </row>
     <row r="4">
@@ -1689,10 +1689,10 @@
         </is>
       </c>
       <c r="D4" s="7" t="n">
-        <v>23510624.77</v>
+        <v>21973160.47</v>
       </c>
       <c r="E4" s="6" t="n">
-        <v>15523.02</v>
+        <v>14507.9</v>
       </c>
     </row>
     <row r="5">
@@ -1712,10 +1712,10 @@
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>18484090.91</v>
+        <v>20418631.26</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>12204.22</v>
+        <v>13481.51</v>
       </c>
     </row>
   </sheetData>
@@ -1777,10 +1777,10 @@
         </is>
       </c>
       <c r="D2" s="7" t="n">
-        <v>26745334.93</v>
+        <v>27118806.31</v>
       </c>
       <c r="E2" s="6" t="n">
-        <v>17658.75</v>
+        <v>17905.34</v>
       </c>
     </row>
     <row r="3">
@@ -1800,10 +1800,10 @@
         </is>
       </c>
       <c r="D3" s="7" t="n">
-        <v>20968753.87</v>
+        <v>21176429.34</v>
       </c>
       <c r="E3" s="6" t="n">
-        <v>13844.73</v>
+        <v>13981.85</v>
       </c>
     </row>
     <row r="4">
@@ -1823,10 +1823,10 @@
         </is>
       </c>
       <c r="D4" s="7" t="n">
-        <v>16313659.94</v>
+        <v>15488635.95</v>
       </c>
       <c r="E4" s="6" t="n">
-        <v>10771.18</v>
+        <v>10226.46</v>
       </c>
     </row>
     <row r="5">
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>17679969.25</v>
+        <v>16497544.35</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>11673.29</v>
+        <v>10892.59</v>
       </c>
     </row>
     <row r="6">
@@ -1869,10 +1869,10 @@
         </is>
       </c>
       <c r="D6" s="7" t="n">
-        <v>19497979.87</v>
+        <v>17266896.81</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>12873.65</v>
+        <v>11400.56</v>
       </c>
     </row>
     <row r="7">
@@ -1892,10 +1892,10 @@
         </is>
       </c>
       <c r="D7" s="7" t="n">
-        <v>19852960.82</v>
+        <v>18070184.65</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>13108.02</v>
+        <v>11930.94</v>
       </c>
     </row>
   </sheetData>
@@ -1953,19 +1953,19 @@
       </c>
       <c r="B2" s="6" t="inlineStr">
         <is>
-          <t>CLI-109</t>
+          <t>CLI-103</t>
         </is>
       </c>
       <c r="C2" s="6" t="inlineStr">
         <is>
-          <t>Hipermercado Andino</t>
+          <t>Almacén El Fogón</t>
         </is>
       </c>
       <c r="D2" s="7" t="n">
-        <v>42430941.31</v>
+        <v>71647230.02</v>
       </c>
       <c r="E2" s="8" t="n">
-        <v>28015.26</v>
+        <v>47305.47</v>
       </c>
       <c r="F2" s="6" t="n">
         <v>1</v>
@@ -1979,19 +1979,19 @@
       </c>
       <c r="B3" s="6" t="inlineStr">
         <is>
-          <t>CLI-101</t>
+          <t>CLI-105</t>
         </is>
       </c>
       <c r="C3" s="6" t="inlineStr">
         <is>
-          <t>Supermercados Don Horacio S.A.</t>
+          <t>Mercado Online Pampero</t>
         </is>
       </c>
       <c r="D3" s="7" t="n">
-        <v>36393991.89</v>
+        <v>65432302.48</v>
       </c>
       <c r="E3" s="8" t="n">
-        <v>24029.33</v>
+        <v>43202.03</v>
       </c>
       <c r="F3" s="6" t="n">
         <v>2</v>
@@ -2005,19 +2005,19 @@
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>CLI-106</t>
+          <t>CLI-102</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>Mayorista San Martín</t>
+          <t>Distribuidora La Ribera S.R.L.</t>
         </is>
       </c>
       <c r="D4" s="7" t="n">
-        <v>35001793.28</v>
+        <v>59515044.12</v>
       </c>
       <c r="E4" s="8" t="n">
-        <v>23110.12</v>
+        <v>39295.13</v>
       </c>
       <c r="F4" s="6" t="n">
         <v>3</v>
@@ -2031,19 +2031,19 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>CLI-105</t>
+          <t>CLI-110</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>Mercado Online Pampero</t>
+          <t>Cadenas del Sur S.A.</t>
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>33152581.38</v>
+        <v>52095575.31</v>
       </c>
       <c r="E5" s="8" t="n">
-        <v>21889.17</v>
+        <v>34396.38</v>
       </c>
       <c r="F5" s="6" t="n">
         <v>4</v>
@@ -2057,19 +2057,19 @@
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>CLI-103</t>
+          <t>CLI-109</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>Almacén El Fogón</t>
+          <t>Hipermercado Andino</t>
         </is>
       </c>
       <c r="D6" s="7" t="n">
-        <v>27902272.21</v>
+        <v>50081774.82</v>
       </c>
       <c r="E6" s="8" t="n">
-        <v>18422.62</v>
+        <v>33066.76</v>
       </c>
       <c r="F6" s="6" t="n">
         <v>5</v>
@@ -2083,19 +2083,19 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>CLI-107</t>
+          <t>CLI-101</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>Cooperativa Valle Verde</t>
+          <t>Supermercados Don Horacio S.A.</t>
         </is>
       </c>
       <c r="D7" s="7" t="n">
-        <v>27275121.78</v>
+        <v>45013475.94</v>
       </c>
       <c r="E7" s="8" t="n">
-        <v>18008.55</v>
+        <v>29720.39</v>
       </c>
       <c r="F7" s="6" t="n">
         <v>6</v>
@@ -2109,19 +2109,19 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>CLI-104</t>
+          <t>CLI-107</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>Grupo Norte Retail S.A.</t>
+          <t>Cooperativa Valle Verde</t>
         </is>
       </c>
       <c r="D8" s="7" t="n">
-        <v>24440362.48</v>
+        <v>41025617.46</v>
       </c>
       <c r="E8" s="8" t="n">
-        <v>16136.88</v>
+        <v>27087.38</v>
       </c>
       <c r="F8" s="6" t="n">
         <v>7</v>
@@ -2135,19 +2135,19 @@
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>CLI-108</t>
+          <t>CLI-106</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>Bodegón Central</t>
+          <t>Mayorista San Martín</t>
         </is>
       </c>
       <c r="D9" s="7" t="n">
-        <v>21003536.08</v>
+        <v>36305744.93</v>
       </c>
       <c r="E9" s="8" t="n">
-        <v>13867.7</v>
+        <v>23971.06</v>
       </c>
       <c r="F9" s="6" t="n">
         <v>8</v>
@@ -2161,19 +2161,19 @@
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>CLI-110</t>
+          <t>CLI-108</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>Cadenas del Sur S.A.</t>
+          <t>Bodegón Central</t>
         </is>
       </c>
       <c r="D10" s="7" t="n">
-        <v>19171811.97</v>
+        <v>27743583.97</v>
       </c>
       <c r="E10" s="8" t="n">
-        <v>12658.29</v>
+        <v>18317.85</v>
       </c>
       <c r="F10" s="6" t="n">
         <v>9</v>
@@ -2187,19 +2187,19 @@
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>CLI-102</t>
+          <t>CLI-104</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>Distribuidora La Ribera S.R.L.</t>
+          <t>Grupo Norte Retail S.A.</t>
         </is>
       </c>
       <c r="D11" s="7" t="n">
-        <v>17687122.39</v>
+        <v>21974831.62</v>
       </c>
       <c r="E11" s="8" t="n">
-        <v>11678.02</v>
+        <v>14509</v>
       </c>
       <c r="F11" s="6" t="n">
         <v>10</v>
